--- a/shucle_report/백운면/20260330_20260405/report_백운면_20260330_20260405.xlsx
+++ b/shucle_report/백운면/20260330_20260405/report_백운면_20260330_20260405.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.30 ~ 04.05 | 비교기간: 2026.03.23 ~ 03.29 | 생성: 2026-04-08 15:25 | 차트: 90개</t>
+          <t>분석기간: 2026.03.30 ~ 04.05 | 비교기간: 2026.03.23 ~ 03.29 | 생성: 2026-04-13 12:24 | 차트: 137개</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>23.9건</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21.9건</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25.1명</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>• 공급 현황: 운행차량 1.0대, 대당 운행시간 8.7시간</t>
+          <t>• 수요 현황: 일평균 호출 23.9건, 이동완료 21.9건, 탑승객 25.1명</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2033,32 +2033,32 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대 이동시간</t>
+          <t>피크 시간대(16~18시) 이동시간</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>11.6→8.0분 감소</t>
         </is>
       </c>
     </row>
@@ -2070,32 +2070,32 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>비피크 시간대 이동시간</t>
+          <t>비피크 시간대(7~9시) 이동시간</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.8</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8.9%</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>8.6→9.4분 증가</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
